--- a/r5-core-xx-fhir-testing/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-xx-fhir-testing/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T08:10:47+00:00</t>
+    <t>2026-10-19T08:31:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-xx-fhir-testing/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-xx-fhir-testing/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T08:31:12+00:00</t>
+    <t>2026-10-19T12:08:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-xx-fhir-testing/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-xx-fhir-testing/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T12:08:07+00:00</t>
+    <t>2026-10-19T12:39:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
